--- a/pack/DirectSportsGoods_forecast.xlsx
+++ b/pack/DirectSportsGoods_forecast.xlsx
@@ -39,14 +39,15 @@
     <definedName name="dep_m">Inputs!$B$29</definedName>
     <definedName name="tax_rate">Inputs!$B$30</definedName>
     <definedName name="fy26_profit">Inputs!$B$31</definedName>
-    <definedName name="cash_open">Inputs!$B$32</definedName>
-    <definedName name="quote">Inputs!$B$35</definedName>
-    <definedName name="switch_cost">Inputs!$B$36</definedName>
-    <definedName name="charge_exvat">Inputs!$B$37</definedName>
-    <definedName name="affected">Inputs!$B$38</definedName>
-    <definedName name="loss">Inputs!$B$39</definedName>
-    <definedName name="price_rise">Inputs!$B$40</definedName>
-    <definedName name="volume_loss">Inputs!$B$41</definedName>
+    <definedName name="large_threshold">Inputs!$B$32</definedName>
+    <definedName name="cash_open">Inputs!$B$33</definedName>
+    <definedName name="quote">Inputs!$B$36</definedName>
+    <definedName name="switch_cost">Inputs!$B$37</definedName>
+    <definedName name="charge_exvat">Inputs!$B$38</definedName>
+    <definedName name="affected">Inputs!$B$39</definedName>
+    <definedName name="loss">Inputs!$B$40</definedName>
+    <definedName name="price_rise">Inputs!$B$41</definedName>
+    <definedName name="volume_loss">Inputs!$B$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -727,13 +728,13 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>7279188.47</v>
+        <v>7188844.15</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>5114622.2</v>
+        <v>5377185.31</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>8652376.02</v>
+        <v>8352889.78</v>
       </c>
     </row>
     <row r="10">
@@ -743,13 +744,13 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>5469360.67</v>
+        <v>5275966.63</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>4447798.93</v>
+        <v>4710362.04</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>5582721.97</v>
+        <v>5402627.9</v>
       </c>
     </row>
     <row r="11">
@@ -759,13 +760,13 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>8326495.48</v>
+        <v>7883243.72</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>4556024.16</v>
+        <v>4818587.27</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>10868037.43</v>
+        <v>10006501.83</v>
       </c>
     </row>
     <row r="12">
@@ -827,7 +828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -1307,7 +1308,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FY26 operating profit (tax paid Nov-26)</t>
+          <t>FY26 operating profit (last two tax instalments due Feb-26 and May-26)</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
@@ -1322,60 +1323,60 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Profit above which tax is paid in quarterly instalments</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>gov.uk, Corporation Tax: paying in instalments</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Cash at 31 January 2026</t>
         </is>
       </c>
-      <c r="B32" s="13" t="n">
-        <v>5541965.71</v>
-      </c>
-      <c r="C32" t="inlineStr">
+      <c r="B33" s="13" t="n">
+        <v>5509424.03</v>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>P1 pack, Cash page</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>Option assumption</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr"/>
-      <c r="E34" s="4" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Option A: second carrier's quoted rate per order</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Fictional quote or company assumption</t>
-        </is>
-      </c>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Option A: one-off cost to switch carrier</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="n">
-        <v>150000</v>
+          <t>Option A: second carrier's quoted rate per order</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="n">
+        <v>4.45</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1386,11 +1387,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Option B: delivery charge per order, ex VAT (£1.99 inc VAT)</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="n">
-        <v>1.6583</v>
+          <t>Option A: one-off cost to switch carrier</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="n">
+        <v>150000</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1401,11 +1402,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Option B: share of website orders below the free-delivery threshold</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="n">
-        <v>0.35</v>
+          <t>Option B: delivery charge per order, ex VAT (£1.99 inc VAT)</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="n">
+        <v>1.6583</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1416,11 +1417,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Option B: share of those orders lost to the charge</t>
+          <t>Option B: share of website orders below the free-delivery threshold</t>
         </is>
       </c>
       <c r="B39" s="12" t="n">
-        <v>0.08</v>
+        <v>0.35</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1431,11 +1432,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Option C: price rise, both channels</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="n">
-        <v>0.02</v>
+          <t>Option B: share of those orders lost to the charge</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="n">
+        <v>0.08</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1446,13 +1447,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Option C: price rise, both channels</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Fictional quote or company assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Option C: orders lost to the price rise</t>
         </is>
       </c>
-      <c r="B41" s="10" t="n">
+      <c r="B42" s="10" t="n">
         <v>0.025</v>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Fictional quote or company assumption</t>
         </is>
@@ -5708,8 +5724,9 @@
           <t>Corporation tax paid</t>
         </is>
       </c>
-      <c r="B54" s="5" t="n">
-        <v>0</v>
+      <c r="B54" s="5">
+        <f>-tax_rate*fy26_profit/4</f>
+        <v/>
       </c>
       <c r="C54" s="5" t="n">
         <v>0</v>
@@ -5717,8 +5734,9 @@
       <c r="D54" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E54" s="5" t="n">
-        <v>0</v>
+      <c r="E54" s="5">
+        <f>-tax_rate*fy26_profit/4</f>
+        <v/>
       </c>
       <c r="F54" s="5" t="n">
         <v>0</v>
@@ -5726,8 +5744,9 @@
       <c r="G54" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="5" t="n">
-        <v>0</v>
+      <c r="H54" s="5">
+        <f>IF(SUM($B$41:$M$41)&gt;large_threshold,-tax_rate*SUM($B$41:$M$41)/4,0)</f>
+        <v/>
       </c>
       <c r="I54" s="5" t="n">
         <v>0</v>
@@ -5736,7 +5755,7 @@
         <v>0</v>
       </c>
       <c r="K54" s="5">
-        <f>-fy26_profit*tax_rate</f>
+        <f>IF(SUM($B$41:$M$41)&gt;large_threshold,-tax_rate*SUM($B$41:$M$41)/4,0)</f>
         <v/>
       </c>
       <c r="L54" s="5" t="n">
@@ -5745,8 +5764,9 @@
       <c r="M54" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N54" s="5" t="n">
-        <v>0</v>
+      <c r="N54" s="5">
+        <f>IF(SUM($B$41:$M$41)&gt;large_threshold,-tax_rate*SUM($B$41:$M$41)/4,0)</f>
+        <v/>
       </c>
       <c r="O54" s="5" t="n">
         <v>0</v>
@@ -5754,8 +5774,9 @@
       <c r="P54" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" s="5" t="n">
-        <v>0</v>
+      <c r="Q54" s="5">
+        <f>IF(SUM($B$41:$M$41)&gt;large_threshold,-tax_rate*SUM($B$41:$M$41)/4,0)</f>
+        <v/>
       </c>
       <c r="R54" s="5" t="n">
         <v>0</v>

--- a/pack/DirectSportsGoods_forecast.xlsx
+++ b/pack/DirectSportsGoods_forecast.xlsx
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>3543259.46</v>
+        <v>4714611.99</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1012478.89</v>
+        <v>2058609.08</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>5216394.85</v>
+        <v>6472795.49</v>
       </c>
     </row>
     <row r="8">
@@ -712,13 +712,13 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>2823259.46</v>
+        <v>3994611.99</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>292478.89</v>
+        <v>1338609.08</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>4496394.85</v>
+        <v>5752795.49</v>
       </c>
     </row>
     <row r="9">
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>7188844.15</v>
+        <v>8913602.619999999</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>5377185.31</v>
+        <v>7123140.51</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>8352889.78</v>
+        <v>10152065.34</v>
       </c>
     </row>
     <row r="10">
@@ -744,13 +744,13 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>5275966.63</v>
+        <v>6163240.79</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>4710362.04</v>
+        <v>5695083.71</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>5402627.9</v>
+        <v>6247029.07</v>
       </c>
     </row>
     <row r="11">
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>7883243.72</v>
+        <v>10032061.63</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>4818587.27</v>
+        <v>7025983.9</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>10006501.83</v>
+        <v>12295953.59</v>
       </c>
     </row>
     <row r="12">
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>0.1046</v>
+        <v>0.0712</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>2360838.34</v>
+        <v>3457287.76</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>5509424.03</v>
+        <v>6346305.21</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U57"/>
+  <dimension ref="A1:U55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2964,7 +2964,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marketing *</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="B16" s="5">
@@ -5878,13 +5878,6 @@
       <c r="U55" s="23">
         <f>S55</f>
         <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>* Marketing uses a placeholder assumption with no citation yet.</t>
-        </is>
       </c>
     </row>
   </sheetData>
